--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/NEW_YORK_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/NEW_YORK_2013.xlsx
@@ -4398,7 +4398,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C225">
@@ -12876,7 +12876,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C696">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C697">
@@ -13686,7 +13686,7 @@
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C741">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C750">
@@ -17466,7 +17466,7 @@
       </c>
       <c r="B951" t="inlineStr">
         <is>
-          <t>General Felipe _Ngeles</t>
+          <t>General Felipe Angeles</t>
         </is>
       </c>
       <c r="C951">
@@ -19345,7 +19345,7 @@
         <v>264</v>
       </c>
       <c r="D1055">
-        <v>0.009051635465954</v>
+        <v>0.009051635465954002</v>
       </c>
     </row>
     <row r="1056">
@@ -21408,7 +21408,7 @@
       </c>
       <c r="B1170" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C1170">
@@ -22254,7 +22254,7 @@
       </c>
       <c r="B1217" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1217">
@@ -24684,7 +24684,7 @@
       </c>
       <c r="B1352" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1352">
